--- a/consent_forms/049_child_vaccine_consent_form--consent_forms.xlsx
+++ b/consent_forms/049_child_vaccine_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -943,8 +943,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -972,12 +972,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'male',_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Male', 'value': 'male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'female',_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Female', 'value': 'female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'mmr_-_measles,_mumps,_rubella',_'value':_'mmr'}</t>
+          <t>mmr_-_measles,_mumps,_rubella</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'MMR - Measles, Mumps, Rubella', 'value': 'mmr'}</t>
+          <t>MMR - Measles, Mumps, Rubella</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'dtap_-_diphtheria,_tetanus,_pertussis',_'value':_'dtap'}</t>
+          <t>dtap_-_diphtheria,_tetanus,_pertussis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'DTaP - Diphtheria, Tetanus, Pertussis', 'value': 'dtap'}</t>
+          <t>DTaP - Diphtheria, Tetanus, Pertussis</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'inactivated_polio_vaccine',_'value':_'polio'}</t>
+          <t>inactivated_polio_vaccine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Inactivated Polio Vaccine', 'value': 'polio'}</t>
+          <t>Inactivated Polio Vaccine</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'hepatitis_b',_'value':_'hepb'}</t>
+          <t>hepatitis_b</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Hepatitis B', 'value': 'hepb'}</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'seasonal_influenza',_'value':_'flu'}</t>
+          <t>seasonal_influenza</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Seasonal Influenza', 'value': 'flu'}</t>
+          <t>Seasonal Influenza</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'varicella_-_chickenpox',_'value':_'varicella'}</t>
+          <t>varicella_-_chickenpox</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Varicella - Chickenpox', 'value': 'varicella'}</t>
+          <t>Varicella - Chickenpox</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_received_and_read',_'value':_true}</t>
+          <t>yes_-_received_and_read</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Received and Read', 'value': True}</t>
+          <t>Yes - Received and Read</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_need_vis_first',_'value':_false}</t>
+          <t>no_-_need_vis_first</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'No - Need VIS first', 'value': False}</t>
+          <t>No - Need VIS first</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'i_give_consent',_'value':_true}</t>
+          <t>i_give_consent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'I Give Consent', 'value': True}</t>
+          <t>I Give Consent</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'i_withhold_consent',_'value':_false}</t>
+          <t>i_withhold_consent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'I Withhold Consent', 'value': False}</t>
+          <t>I Withhold Consent</t>
         </is>
       </c>
     </row>
